--- a/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION_SECONDPRODUCT.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION_SECONDPRODUCT.xlsx
@@ -167,8 +167,7 @@
     </font>
     <font>
       <name val="Times New Roman"/>
-      <b val="1"/>
-      <color theme="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -400,7 +399,7 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -707,15 +706,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
     <col width="19" customWidth="1" style="19" min="2" max="2"/>
     <col width="30.6640625" bestFit="1" customWidth="1" style="15" min="3" max="3"/>
-    <col width="36.6640625" bestFit="1" customWidth="1" style="16" min="4" max="4"/>
-    <col width="59.5" customWidth="1" style="19" min="5" max="5"/>
-    <col width="59.1640625" customWidth="1" style="16" min="6" max="6"/>
+    <col width="69.1640625" customWidth="1" style="16" min="4" max="4"/>
+    <col width="90.1640625" customWidth="1" style="19" min="5" max="5"/>
+    <col width="90.1640625" customWidth="1" style="16" min="6" max="6"/>
     <col width="9.1640625" customWidth="1" style="19" min="7" max="16384"/>
   </cols>
   <sheetData>
@@ -732,10 +731,9 @@
       </c>
       <c r="E1" s="52" t="inlineStr">
         <is>
-          <t>NG_SB_RLOS_SUB_PRODUCT AS A</t>
-        </is>
-      </c>
-      <c r="F1" s="52" t="n"/>
+          <t>STG_FCT_RLOS_APPLICATION_SECONDPRODUCT AS A</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
@@ -745,15 +743,10 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Bảng Fact đăng ký sản phẩm phụ của hồ sơ RLOS, driving từ NG_SB_RLOS_SUB_PRODUCT</t>
-        </is>
-      </c>
-      <c r="E2" s="52" t="inlineStr">
-        <is>
-          <t>DIM_RLOS_APPLICATION AS B</t>
-        </is>
-      </c>
-      <c r="F2" s="52" t="n"/>
+          <t>Relay 1:1 từ STG_DTM.STG_FCT_RLOS_APPLICATION_SECONDPRODUCT sang PDTD_DTM, không aggregation thêm</t>
+        </is>
+      </c>
+      <c r="E2" s="52" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -766,12 +759,7 @@
           <t>DAYID + SUB_PRODUCT_BK</t>
         </is>
       </c>
-      <c r="E3" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_APPLICANT_GENERAL AS C</t>
-        </is>
-      </c>
-      <c r="F3" s="52" t="n"/>
+      <c r="E3" s="52" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -784,82 +772,47 @@
           <t>Chạy dữ liệu FULL hàng ngày</t>
         </is>
       </c>
-      <c r="E4" s="52" t="inlineStr">
-        <is>
-          <t>DIM_RLOS_SECONDPRODUCT AS D</t>
-        </is>
-      </c>
-      <c r="F4" s="52" t="n"/>
+      <c r="E4" s="52" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
-      <c r="E5" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_CREDIT_CARD_APP AS E</t>
-        </is>
-      </c>
-      <c r="F5" s="52" t="n"/>
+      <c r="E5" s="52" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
-      <c r="E6" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_SEABUY_APP AS F</t>
-        </is>
-      </c>
-      <c r="F6" s="52" t="n"/>
+      <c r="E6" s="52" t="n"/>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
-      <c r="E7" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_CIVIL_APP AS G</t>
-        </is>
-      </c>
-      <c r="F7" s="52" t="n"/>
+      <c r="E7" s="52" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
-      <c r="E8" s="52" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_TEACHER_APP AS H</t>
-        </is>
-      </c>
-      <c r="F8" s="53" t="n"/>
+      <c r="E8" s="52" t="n"/>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
-      <c r="E9" s="53" t="inlineStr">
-        <is>
-          <t>NG_SB_RLOS_WOMAN_APP AS I</t>
-        </is>
-      </c>
-      <c r="F9" s="52" t="n"/>
+      <c r="E9" s="53" t="n"/>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
       <c r="E10" s="53" t="n"/>
-      <c r="F10" s="52" t="n"/>
     </row>
     <row r="11" hidden="1">
       <c r="A11" s="13" t="n"/>
       <c r="E11" s="53" t="n"/>
-      <c r="F11" s="52" t="n"/>
     </row>
     <row r="12" hidden="1">
       <c r="A12" s="13" t="n"/>
       <c r="E12" s="53" t="n"/>
-      <c r="F12" s="52" t="n"/>
     </row>
     <row r="13" hidden="1">
       <c r="A13" s="13" t="n"/>
       <c r="E13" s="53" t="n"/>
-      <c r="F13" s="52" t="n"/>
     </row>
     <row r="14" hidden="1">
       <c r="A14" s="13" t="n"/>
       <c r="E14" s="53" t="n"/>
-      <c r="F14" s="53" t="n"/>
     </row>
     <row r="15" ht="17" customHeight="1">
       <c r="A15" s="1" t="inlineStr">
@@ -887,9 +840,8 @@
           <t>How to mapping RLOS</t>
         </is>
       </c>
-      <c r="F15" s="1" t="n"/>
-    </row>
-    <row r="16" ht="51" customHeight="1">
+    </row>
+    <row r="16">
       <c r="A16" s="6" t="n"/>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="7" t="n"/>
@@ -899,9 +851,8 @@
         </is>
       </c>
       <c r="E16" s="6" t="n"/>
-      <c r="F16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -917,17 +868,16 @@
           <t>Ngày dữ liệu</t>
         </is>
       </c>
-      <c r="D17" s="27" t="inlineStr">
-        <is>
-          <t>PK — Driving: NG_SB_RLOS_SUB_PRODUCT. Ngày dữ liệu, dạng số YYYYMMDD</t>
-        </is>
-      </c>
-      <c r="E17" s="28" t="inlineStr">
-        <is>
-          <t>v_batch_date</t>
-        </is>
-      </c>
-      <c r="F17" s="28" t="n"/>
+      <c r="D17" s="54" t="inlineStr">
+        <is>
+          <t>PK (1/2) — Driving: STG_FCT_RLOS_APPLICATION_SECONDPRODUCT. Ngày dữ liệu, dạng số YYYYMMDD</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>A.DAYID</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
@@ -945,17 +895,16 @@
           <t>Khóa nghiệp vụ</t>
         </is>
       </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>Khóa nghiệp vụ của 1 lần đăng ký sản phẩm phụ. PK chỉ cần DAYID+SUB_PRODUCT_BK, không cần thêm WI_NAME/SUB_PRODUCT_LINE làm thành phần PK riêng. NG_SB_RLOS_SUB_PRODUCT không khai KEY CDC, vẫn phải hash. [CẦN REVIEW] Rủi ro đụng độ (2 thẻ phụ cùng hồ sơ trùng cả SPP_AMOUNT lẫn SPP_TERM) — CHẤP NHẬN theo quyết định người dùng</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="inlineStr">
-        <is>
-          <t>STANDARD_HASH(A.WI_NAME || A.SUB_PRODUCT_LINE || NVL(TO_CHAR(E.SPP_AMOUNT),'&lt;NULL&gt;') || NVL(TO_CHAR(E.SPP_TERM),'&lt;NULL&gt;')|| E.RECID, 'MD5')</t>
-        </is>
-      </c>
-      <c r="F18" s="28" t="n"/>
+      <c r="D18" s="54" t="inlineStr">
+        <is>
+          <t>PK (2/2) — Khóa nghiệp vụ của 1 lần đăng ký sản phẩm phụ</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>A.SUB_PRODUCT_BK</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
@@ -973,19 +922,18 @@
           <t>Khóa tới hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại — tra DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1 nếu không khớp</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="inlineStr">
-        <is>
-          <t>B.DIMENSION_KEY</t>
-        </is>
-      </c>
-      <c r="F19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customFormat="1" customHeight="1" s="20">
+      <c r="D19" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_APPLICATION</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>A.APPLICATION_SK</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
           <t>SECONDPRODUCT_SK</t>
@@ -1001,17 +949,16 @@
           <t>Khóa tới sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D20" s="27" t="inlineStr">
-        <is>
-          <t>Khóa ngoại MỚI (review 2026-10-04, theo yêu cầu người dùng) — tra DIM_RLOS_SECONDPRODUCT theo phiên bản hiệu lực tại DAYID [CẦN REVIEW] Mặc định -1 nếu hồ sơ không có sản phẩm phụ hoặc không khớp. SUB_PRODUCT_LINE lấy từ chính dòng NG_SB_RLOS_SUB_PRODUCT</t>
-        </is>
-      </c>
-      <c r="E20" s="28" t="inlineStr">
-        <is>
-          <t>D.DIMENSION_KEY</t>
-        </is>
-      </c>
-      <c r="F20" s="28" t="n"/>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Khóa tới DIM_RLOS_SECONDPRODUCT — MỚI</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>A.SECONDPRODUCT_SK</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="28" t="inlineStr">
@@ -1029,17 +976,16 @@
           <t>Mã hồ sơ tín dụng</t>
         </is>
       </c>
-      <c r="D21" s="27" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng RLOS. Driving table, khớp SRS BC1 BR 1.2 — 1 dòng = 1 hồ sơ x 1 lần đăng ký sản phẩm phụ</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
         <is>
           <t>A.WI_NAME</t>
         </is>
       </c>
-      <c r="F21" s="28" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="28" t="inlineStr">
@@ -1057,17 +1003,16 @@
           <t>Dòng sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D22" s="27" t="inlineStr">
-        <is>
-          <t>Dòng của sản phẩm phụ. Trường SAN_PHAM_PHU của BC1 — 5 giá trị khả dĩ ('SeABuy'/'SeACivil'/'SeATeacher'/'SeAWomen'/'Thẻ tín dụng') tự phân biệt loại sản phẩm phụ, đủ dùng làm điều kiện JOIN sang 5 bảng grid, đồng thời là đầu vào tra SECONDPRODUCT_SK</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>Dòng của sản phẩm phụ</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
         <is>
           <t>A.SUB_PRODUCT_LINE</t>
         </is>
       </c>
-      <c r="F22" s="28" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="28" t="inlineStr">
@@ -1085,17 +1030,16 @@
           <t>Hạn mức sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D23" s="27" t="inlineStr">
-        <is>
-          <t>Hạn mức của sản phẩm phụ. Trường SPP_Amount của BC1. PHÁI SINH theo SRS BC1 BR 1.2: LEFT JOIN đúng 1 trong 5 bảng grid theo WI_NAME AND SUB_PRODUCT_LINE=&lt;giá trị tương ứng&gt; (KHÔNG phải UNION 5 nguồn độc lập), lấy LIMIT_NO của đúng bảng đã khớp. Chỉ đúng 1 trong 5 JOIN khớp tại mỗi dòng (loại trừ lẫn nhau theo SUB_PRODUCT_LINE)</t>
-        </is>
-      </c>
-      <c r="E23" s="28" t="inlineStr">
-        <is>
-          <t>COALESCE(E.LIMIT_NO, F.LIMIT_NO, G.LIMIT_NO, H.LIMIT_NO, TO_NUMBER(REPLACE(I.LIMIT_NO, ',', '') DEFAULT NULL ON CONVERSION ERROR))</t>
-        </is>
-      </c>
-      <c r="F23" s="28" t="n"/>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>Hạn mức của sản phẩm phụ</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>A.SPP_AMOUNT</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="28" t="inlineStr">
@@ -1113,19 +1057,18 @@
           <t>Thời hạn sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D24" s="27" t="inlineStr">
-        <is>
-          <t>Thời hạn của sản phẩm phụ, đơn vị tháng. Trường SPP_Term của BC1. PHÁI SINH, cùng cơ chế JOIN với SPP_AMOUNT: CREDIT_CARD_APP.TERM hoặc SEABUY_APP/CIVIL_APP/TEACHER_APP/WOMAN_APP.TIME_VALID của đúng bảng đã khớp điều kiện JOIN</t>
-        </is>
-      </c>
-      <c r="E24" s="28" t="inlineStr">
-        <is>
-          <t>COALESCE(E.TERM, F.TIME_VALID, G.TIME_VALID, H.TIME_VALID, I.TIME_VALID)</t>
-        </is>
-      </c>
-      <c r="F24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>Thời hạn của sản phẩm phụ, đơn vị tháng</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>A.SPP_TERM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="75" customHeight="1">
       <c r="A25" s="28" t="inlineStr">
         <is>
           <t>CARD_TYPE_CODE</t>
@@ -1141,248 +1084,17 @@
           <t>Loại thẻ đăng ký</t>
         </is>
       </c>
-      <c r="D25" s="27" t="inlineStr">
-        <is>
-          <t>Loại thẻ đăng ký lúc đề xuất sản phẩm phụ là thẻ tín dụng. Chỉ có ở dòng SUB_PRODUCT_LINE='Thẻ tín dụng'. Là khái niệm khác BC1.K_TYPE (loại thẻ thật sau giải ngân, thuộc FCT_RLOS_APPLICATION, không đi qua bảng này)</t>
-        </is>
-      </c>
-      <c r="E25" s="28" t="inlineStr">
-        <is>
-          <t>E.CARD_TYPE</t>
-        </is>
-      </c>
-      <c r="F25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="51" customHeight="1"/>
-    <row r="27" ht="16" customHeight="1">
-      <c r="A27" s="10" t="n"/>
-      <c r="B27" s="10" t="n"/>
-      <c r="C27" s="10" t="n"/>
-      <c r="D27" s="54" t="inlineStr">
-        <is>
-          <t>Điều kiện join giữa các bảng</t>
-        </is>
-      </c>
-      <c r="E27" s="10" t="n"/>
-      <c r="F27" s="10" t="n"/>
-    </row>
-    <row r="28" ht="45" customHeight="1">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="51" t="n"/>
-      <c r="D28" s="8" t="n"/>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="25" t="n"/>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="51" t="n"/>
-      <c r="D29" s="8" t="n"/>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN C.WI_NAME = A.WI_NAME</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n"/>
-    </row>
-    <row r="30" ht="60" customHeight="1">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="51" t="n"/>
-      <c r="D30" s="8" t="n"/>
-      <c r="E30" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN D.PRODUCTLINE_CODE = C.PRODUCT_LINE AND D.SECONDARY_PRODUCT = A.SUB_PRODUCT_LINE AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
-        </is>
-      </c>
-      <c r="F30" s="8" t="n"/>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="25" t="n"/>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="51" t="n"/>
-      <c r="D31" s="8" t="n"/>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN E.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'Thẻ tín dụng'</t>
-        </is>
-      </c>
-      <c r="F31" s="8" t="n"/>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="51" t="n"/>
-      <c r="D32" s="8" t="n"/>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeABuy'</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="51" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN G.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeACivil'</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n"/>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="51" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN H.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeATeacher'</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="25" t="n"/>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="51" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>LEFT JOIN I.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeAWomen'</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n"/>
-    </row>
-    <row r="36" ht="17" customHeight="1"/>
-    <row r="37" ht="51" customHeight="1"/>
-    <row r="38" ht="51" customHeight="1"/>
-    <row r="39" ht="34" customHeight="1"/>
-    <row r="40" ht="34" customHeight="1"/>
-    <row r="41" ht="34" customHeight="1"/>
-    <row r="42" ht="17" customHeight="1"/>
-    <row r="43" ht="34" customHeight="1"/>
-    <row r="44" ht="17" customHeight="1"/>
-    <row r="45" ht="85" customHeight="1"/>
-    <row r="46" ht="34" customHeight="1"/>
-    <row r="47" ht="17" customHeight="1"/>
-    <row r="48" ht="17" customHeight="1"/>
-    <row r="49" ht="17" customHeight="1"/>
-    <row r="50" ht="51" customHeight="1"/>
-    <row r="51" ht="51" customHeight="1"/>
-    <row r="52" ht="34" customHeight="1"/>
-    <row r="53" ht="34" customHeight="1"/>
-    <row r="54" ht="34" customHeight="1"/>
-    <row r="55" ht="34" customHeight="1"/>
-    <row r="56" ht="68" customHeight="1"/>
-    <row r="57" ht="51" customHeight="1"/>
-    <row r="58" ht="34" customHeight="1"/>
-    <row r="59" ht="17" customHeight="1"/>
-    <row r="60" ht="34" customHeight="1"/>
-    <row r="61" ht="17" customHeight="1"/>
-    <row r="62" ht="85" customHeight="1"/>
-    <row r="63" ht="85" customHeight="1"/>
-    <row r="64" ht="34" customHeight="1"/>
-    <row r="65" ht="17" customHeight="1"/>
-    <row r="66" ht="34" customHeight="1"/>
-    <row r="67" ht="51" customHeight="1"/>
-    <row r="68" ht="51" customHeight="1"/>
-    <row r="69" ht="51" customHeight="1"/>
-    <row r="70" ht="17" customHeight="1"/>
-    <row r="71" ht="34" customHeight="1"/>
-    <row r="72" ht="34" customHeight="1"/>
-    <row r="73" ht="34" customHeight="1"/>
-    <row r="74" ht="34" customHeight="1"/>
-    <row r="75" ht="34" customHeight="1"/>
-    <row r="76" ht="34" customHeight="1"/>
-    <row r="77" ht="51" customHeight="1"/>
-    <row r="78" ht="34" customHeight="1"/>
-    <row r="79" ht="51" customHeight="1"/>
-    <row r="80" ht="17" customHeight="1"/>
-    <row r="81" ht="17" customHeight="1"/>
-    <row r="82" ht="17" customHeight="1"/>
-    <row r="83" ht="17" customHeight="1"/>
-    <row r="84" ht="17" customHeight="1"/>
-    <row r="85" ht="17" customHeight="1"/>
-    <row r="86" ht="17" customHeight="1"/>
-    <row r="87" ht="17" customHeight="1"/>
-    <row r="88" ht="17" customHeight="1"/>
-    <row r="89" ht="17" customHeight="1"/>
-    <row r="90" ht="34" customHeight="1"/>
-    <row r="91" ht="17" customHeight="1"/>
-    <row r="92" ht="17" customHeight="1"/>
-    <row r="93" ht="17" customHeight="1"/>
-    <row r="94" ht="17" customHeight="1"/>
-    <row r="95" ht="17" customHeight="1"/>
-    <row r="96" ht="17" customHeight="1"/>
-    <row r="97" ht="17" customHeight="1"/>
-    <row r="100" ht="187" customHeight="1"/>
-    <row r="101" ht="17" customHeight="1"/>
-    <row r="102" ht="17" customHeight="1"/>
-    <row r="103" ht="17" customHeight="1"/>
-    <row r="104" ht="17" customHeight="1"/>
-    <row r="105" ht="17" customHeight="1"/>
-    <row r="106" ht="17" customHeight="1"/>
-    <row r="107" ht="17" customHeight="1"/>
-    <row r="108" ht="17" customHeight="1"/>
-    <row r="109" ht="17" customHeight="1"/>
-    <row r="110" ht="17" customHeight="1"/>
-    <row r="111" ht="17" customHeight="1"/>
-    <row r="112" ht="17" customHeight="1"/>
-    <row r="113" ht="17" customHeight="1"/>
-    <row r="114" ht="17" customHeight="1"/>
-    <row r="115" ht="17" customHeight="1"/>
-    <row r="116" ht="17" customHeight="1"/>
-    <row r="117" ht="17" customHeight="1"/>
-    <row r="118" ht="17" customHeight="1"/>
-    <row r="119" ht="17" customHeight="1"/>
-    <row r="120" ht="68" customHeight="1"/>
-    <row r="121" ht="51" customHeight="1"/>
-    <row r="122" ht="34" customHeight="1"/>
-    <row r="123" ht="153" customHeight="1"/>
-    <row r="124" ht="17" customHeight="1"/>
-    <row r="125" ht="17" customHeight="1"/>
-    <row r="132" ht="60" customHeight="1"/>
-    <row r="133" ht="17" customHeight="1"/>
-    <row r="134" ht="17" customHeight="1"/>
-    <row r="135" ht="17" customHeight="1"/>
-    <row r="136" ht="17" customHeight="1"/>
-    <row r="137" ht="51" customHeight="1"/>
-    <row r="138" ht="45" customHeight="1"/>
-    <row r="139" ht="120" customHeight="1"/>
-    <row r="141" ht="384" customHeight="1"/>
-    <row r="143" ht="34" customHeight="1"/>
-    <row r="148" ht="119" customHeight="1"/>
-    <row r="149" ht="17" customHeight="1"/>
-    <row r="150" ht="17" customHeight="1"/>
-    <row r="151" ht="17" customHeight="1"/>
-    <row r="152" ht="51" customHeight="1"/>
-    <row r="153" ht="34" customHeight="1"/>
-    <row r="154" ht="30" customHeight="1"/>
-    <row r="155" ht="17" customHeight="1"/>
-    <row r="157" ht="119" customHeight="1"/>
-    <row r="158" ht="17" customHeight="1"/>
-    <row r="159" ht="17" customHeight="1"/>
-    <row r="160" ht="17" customHeight="1"/>
-    <row r="161" ht="17" customHeight="1"/>
-    <row r="162" ht="17" customHeight="1"/>
-    <row r="163" ht="17" customHeight="1"/>
-    <row r="164" ht="17" customHeight="1"/>
-    <row r="165" ht="17" customHeight="1"/>
-    <row r="166" ht="34" customHeight="1"/>
-    <row r="167" ht="34" customHeight="1"/>
-    <row r="168" ht="16" customHeight="1"/>
-    <row r="169" ht="17" customHeight="1"/>
-    <row r="170" ht="17" customHeight="1"/>
-    <row r="2480" customFormat="1" s="19"/>
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>Loại thẻ đăng ký lúc đề xuất sản phẩm phụ là thẻ tín dụng, chỉ có giá trị ở dòng SUB_PRODUCT_LINE='Thẻ tín dụng' — khác khái niệm BC1.K_TYPE (loại thẻ thật sau giải ngân, nguồn STG_DIM_CARD.K_TYPE qua NG_SB_RLOS_SENT_CBS_LOG, ngoài phạm vi datamart hiện tại)</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>A.CARD_TYPE_CODE</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION_SECONDPRODUCT.xlsx
+++ b/mapping/SB_DWH/Mapping_FCT_RLOS_APPLICATION_SECONDPRODUCT.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -168,6 +168,15 @@
     <font>
       <name val="Times New Roman"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="5">
@@ -238,7 +247,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -400,6 +409,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -706,7 +718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="16"/>
   <cols>
     <col width="34.33203125" customWidth="1" style="19" min="1" max="1"/>
@@ -731,7 +743,7 @@
       </c>
       <c r="E1" s="52" t="inlineStr">
         <is>
-          <t>STG_FCT_RLOS_APPLICATION_SECONDPRODUCT AS A</t>
+          <t>NG_SB_RLOS_SUB_PRODUCT AS A</t>
         </is>
       </c>
     </row>
@@ -743,10 +755,14 @@
       </c>
       <c r="B2" s="19" t="inlineStr">
         <is>
-          <t>Relay 1:1 từ STG_DTM.STG_FCT_RLOS_APPLICATION_SECONDPRODUCT sang PDTD_DTM, không aggregation thêm</t>
-        </is>
-      </c>
-      <c r="E2" s="52" t="n"/>
+          <t>Bảng FACT lưu chi tiết từng lần đăng ký sản phẩm phụ đi kèm hồ sơ tín dụng RLOS (SeABuy, SeACivil, SeATeacher, SeAWomen, thẻ tín dụng phụ)</t>
+        </is>
+      </c>
+      <c r="E2" s="52" t="inlineStr">
+        <is>
+          <t>DIM_RLOS_APPLICATION AS B</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="inlineStr">
@@ -759,7 +775,11 @@
           <t>DAYID + SUB_PRODUCT_BK</t>
         </is>
       </c>
-      <c r="E3" s="52" t="n"/>
+      <c r="E3" s="52" t="inlineStr">
+        <is>
+          <t>NG_SB_RLOS_APPLICANT_GENERAL AS C</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
@@ -772,27 +792,51 @@
           <t>Chạy dữ liệu FULL hàng ngày</t>
         </is>
       </c>
-      <c r="E4" s="52" t="n"/>
+      <c r="E4" s="52" t="inlineStr">
+        <is>
+          <t>DIM_RLOS_SECONDPRODUCT AS D</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="n"/>
-      <c r="E5" s="52" t="n"/>
+      <c r="E5" s="52" t="inlineStr">
+        <is>
+          <t>NG_SB_RLOS_CREDIT_CARD_APP AS E</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="n"/>
-      <c r="E6" s="52" t="n"/>
+      <c r="E6" s="52" t="inlineStr">
+        <is>
+          <t>NG_SB_RLOS_SEABUY_APP AS F</t>
+        </is>
+      </c>
     </row>
     <row r="7" hidden="1">
       <c r="A7" s="13" t="n"/>
-      <c r="E7" s="52" t="n"/>
+      <c r="E7" s="52" t="inlineStr">
+        <is>
+          <t>NG_SB_RLOS_CIVIL_APP AS G</t>
+        </is>
+      </c>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="13" t="n"/>
-      <c r="E8" s="52" t="n"/>
+      <c r="E8" s="52" t="inlineStr">
+        <is>
+          <t>NG_SB_RLOS_TEACHER_APP AS H</t>
+        </is>
+      </c>
     </row>
     <row r="9" hidden="1">
       <c r="A9" s="13" t="n"/>
-      <c r="E9" s="53" t="n"/>
+      <c r="E9" s="53" t="inlineStr">
+        <is>
+          <t>NG_SB_RLOS_WOMAN_APP AS I</t>
+        </is>
+      </c>
     </row>
     <row r="10" hidden="1">
       <c r="A10" s="13" t="n"/>
@@ -852,7 +896,7 @@
       </c>
       <c r="E16" s="6" t="n"/>
     </row>
-    <row r="17" ht="45" customHeight="1">
+    <row r="17" ht="15" customHeight="1">
       <c r="A17" s="28" t="inlineStr">
         <is>
           <t>DAYID</t>
@@ -870,16 +914,16 @@
       </c>
       <c r="D17" s="54" t="inlineStr">
         <is>
-          <t>PK (1/2) — Driving: STG_FCT_RLOS_APPLICATION_SECONDPRODUCT. Ngày dữ liệu, dạng số YYYYMMDD</t>
+          <t>Ngày dữ liệu, dạng số YYYYMMDD</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>A.DAYID</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
+          <t>v_batch_date</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="195" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT_BK</t>
@@ -892,21 +936,21 @@
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Khóa nghiệp vụ</t>
+          <t>Khóa nghiệp vụ sản phẩm phụ</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>PK (2/2) — Khóa nghiệp vụ của 1 lần đăng ký sản phẩm phụ</t>
+          <t>Khóa nghiệp vụ của 1 lần đăng ký sản phẩm phụ. PK chỉ cần DAYID+SUB_PRODUCT_BK, không cần thêm WI_NAME/SUB_PRODUCT_LINE làm thành phần PK riêng. A không khai KEY CDC (DS_BANG_202608.xlsx rỗng), vẫn phải hash. Hash cặp khóa driving table (WI_NAME+SUB_PRODUCT_LINE) cộng 2 giá trị đã JOIN bổ sung (SPP_AMOUNT/SPP_TERM, tính sau ở 2 dòng dưới) để phân biệt nhiều dòng thẻ phụ nhân ra khi LEFT JOIN CREDIT_CARD_APP khớp nhiều thẻ/hồ sơ. KHÔNG hash CARD_TYPE_CODE và KHÔNG hash toàn bộ cột của 5 bảng grid. Rủi ro đụng độ (2 thẻ phụ cùng hồ sơ trùng cả SPP_AMOUNT lẫn SPP_TERM) — CHẤP NHẬN theo quyết định người dùng, cùng bản chất rủi ro đã chấp nhận ở FCT_CLOS_DEVIATION/FCT_RLOS_DEVIATION.</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>A.SUB_PRODUCT_BK</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1">
+          <t>STANDARD_HASH(A.WI_NAME || A.SUB_PRODUCT_LINE || NVL(TO_CHAR(E.SPP_AMOUNT),'&lt;NULL&gt;') || NVL(TO_CHAR(E.SPP_TERM),'&lt;NULL&gt;')|| E.RECID, 'MD5')</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
       <c r="A19" s="28" t="inlineStr">
         <is>
           <t>APPLICATION_SK</t>
@@ -919,179 +963,332 @@
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Khóa tới hồ sơ tín dụng</t>
+          <t>Khóa hồ sơ tín dụng</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>Khóa tới DIM_RLOS_APPLICATION</t>
+          <t>Khóa ngoại — tra DIM_RLOS_APPLICATION theo phiên bản hiệu lực tại DAYID. Mặc định -1 nếu không khớp</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>A.APPLICATION_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+          <t>B.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
       <c r="A20" s="28" t="inlineStr">
         <is>
+          <t>WI_NAME</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(100)</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>Mã hồ sơ tín dụng RLOS. Driving table, khớp SRS BC1 BR 1.2 — 1 dòng = 1 hồ sơ x 1 lần đăng ký sản phẩm phụ.</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="60" customHeight="1">
+      <c r="A21" s="28" t="inlineStr">
+        <is>
           <t>SECONDPRODUCT_SK</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B21" s="25" t="inlineStr">
         <is>
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>Khóa tới sản phẩm phụ</t>
-        </is>
-      </c>
-      <c r="D20" s="54" t="inlineStr">
-        <is>
-          <t>Khóa tới DIM_RLOS_SECONDPRODUCT — MỚI</t>
-        </is>
-      </c>
-      <c r="E20" s="31" t="inlineStr">
-        <is>
-          <t>A.SECONDPRODUCT_SK</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>WI_NAME</t>
-        </is>
-      </c>
-      <c r="B21" s="25" t="inlineStr">
+      <c r="C21" s="26" t="inlineStr">
+        <is>
+          <t>Khóa sản phẩm phụ</t>
+        </is>
+      </c>
+      <c r="D21" s="54" t="inlineStr">
+        <is>
+          <t>Khóa ngoại MỚI — tra DIM_RLOS_SECONDPRODUCT theo phiên bản hiệu lực tại DAYID. Mặc định -1 nếu hồ sơ không có sản phẩm phụ hoặc không khớp. SUB_PRODUCT_LINE lấy từ chính dòng A (cùng nguồn cột SUB_PRODUCT_LINE bên dưới)</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>D.DIMENSION_KEY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>PRODUCTLINE_CODE</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C21" s="26" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng</t>
-        </is>
-      </c>
-      <c r="D21" s="54" t="inlineStr">
-        <is>
-          <t>Mã hồ sơ tín dụng RLOS</t>
-        </is>
-      </c>
-      <c r="E21" s="31" t="inlineStr">
-        <is>
-          <t>A.WI_NAME</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="28" t="inlineStr">
+      <c r="C22" s="26" t="inlineStr">
+        <is>
+          <t>Mã sản phẩm chính</t>
+        </is>
+      </c>
+      <c r="D22" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: 1 phần BK composite (PRODUCTLINE_CODE+SECONDARY_PRODUCT) của DIM_RLOS_SECONDPRODUCT, sản phẩm chính của hồ sơ</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>C.PRODUCT_LINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="105" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>SECONDARY_PRODUCT</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>VARCHAR2(200)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="inlineStr">
+        <is>
+          <t>Mã sản phẩm phụ (BK)</t>
+        </is>
+      </c>
+      <c r="D23" s="54" t="inlineStr">
+        <is>
+          <t>CỘT MỚI — BK cạnh SK: nửa còn lại BK composite DIM_RLOS_SECONDPRODUCT, cùng giá trị với SUB_PRODUCT_LINE (đã dùng làm điều kiện JOIN SECONDARY_PRODUCT=SUB_PRODUCT_LINE). Giữ tên gọi đúng theo BK gốc của DIM (SECONDARY_PRODUCT) để tách biệt ý nghĩa khóa nghiệp vụ khỏi cột nghiệp vụ gốc (SUB_PRODUCT_LINE, cột liền sau).</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>A.SUB_PRODUCT_LINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="90" customHeight="1">
+      <c r="A24" s="28" t="inlineStr">
         <is>
           <t>SUB_PRODUCT_LINE</t>
         </is>
       </c>
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(200)</t>
         </is>
       </c>
-      <c r="C22" s="26" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Dòng sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D22" s="54" t="inlineStr">
-        <is>
-          <t>Dòng của sản phẩm phụ</t>
-        </is>
-      </c>
-      <c r="E22" s="31" t="inlineStr">
+      <c r="D24" s="54" t="inlineStr">
+        <is>
+          <t>Dòng của sản phẩm phụ. Trường SAN_PHAM_PHU của BC1 — 5 giá trị khả dĩ ('SeABuy'/'SeACivil'/'SeATeacher'/'SeAWomen'/'Thẻ tín dụng') tự phân biệt loại sản phẩm phụ, đủ dùng làm điều kiện JOIN sang 5 bảng grid, đồng thời là đầu vào tra SECONDPRODUCT_SK. SUB_PRODUCT_TYPE_CODE không có trong thiết kế — chỉ là ánh xạ 1-1 dư thừa của cột này.</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
         <is>
           <t>A.SUB_PRODUCT_LINE</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
+    <row r="25" ht="135" customHeight="1">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>SPP_AMOUNT</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>NUMBER(20,2)</t>
         </is>
       </c>
-      <c r="C23" s="26" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Hạn mức sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D23" s="54" t="inlineStr">
-        <is>
-          <t>Hạn mức của sản phẩm phụ</t>
-        </is>
-      </c>
-      <c r="E23" s="31" t="inlineStr">
-        <is>
-          <t>A.SPP_AMOUNT</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="28" t="inlineStr">
+      <c r="D25" s="54" t="inlineStr">
+        <is>
+          <t>Hạn mức của sản phẩm phụ. Trường SPP_Amount của BC1. PHÁI SINH, theo SRS BC1 BR 1.2: LEFT JOIN đúng 1 trong 5 bảng grid theo WI_NAME=WI_NAME AND SUB_PRODUCT_LINE=&lt;giá trị tương ứng&gt; (KHÔNG phải UNION 5 nguồn độc lập), lấy LIMIT_NO của đúng bảng đã khớp. Dữ liệu mẫu thực tế hỗn hợp (số nguyên thuần, hoặc có dấu phẩy ngăn nghìn + dấu chấm thập phân kiểu Anh-Mỹ, hoặc text không phải số) — bỏ dấu phẩy trước khi TO_NUMBER, DEFAULT NULL ON CONVERSION ERROR tự trả NULL cho text. Chỉ đúng 1 trong 5 JOIN khớp tại mỗi dòng (loại trừ lẫn nhau theo SUB_PRODUCT_LINE).</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>CASE A.SUB_PRODUCT_LINE WHEN 'Thẻ tín dụng' THEN TO_NUMBER(REPLACE(E.LIMIT_NO, ',', '') DEFAULT NULL ON CONVERSION ERROR) WHEN 'SeABuy' THEN TO_NUMBER(REPLACE(F.LIMIT_NO, ',', '') DEFAULT NULL ON CONVERSION ERROR) WHEN 'SeACivil' THEN TO_NUMBER(REPLACE(G.LIMIT_NO, ',', '') DEFAULT NULL ON CONVERSION ERROR) WHEN 'SeATeacher' THEN TO_NUMBER(REPLACE(H.LIMIT_NO, ',', '') DEFAULT NULL ON CONVERSION ERROR) WHEN 'SeAWomen' THEN TO_NUMBER(REPLACE(I.LIMIT_NO, ',', '') DEFAULT NULL ON CONVERSION ERROR) END</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="28" t="inlineStr">
         <is>
           <t>SPP_TERM</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B26" s="25" t="inlineStr">
         <is>
           <t>NUMBER(5)</t>
         </is>
       </c>
-      <c r="C24" s="26" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Thời hạn sản phẩm phụ</t>
         </is>
       </c>
-      <c r="D24" s="54" t="inlineStr">
-        <is>
-          <t>Thời hạn của sản phẩm phụ, đơn vị tháng</t>
-        </is>
-      </c>
-      <c r="E24" s="31" t="inlineStr">
-        <is>
-          <t>A.SPP_TERM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="75" customHeight="1">
-      <c r="A25" s="28" t="inlineStr">
+      <c r="D26" s="54" t="inlineStr">
+        <is>
+          <t>Thời hạn của sản phẩm phụ, đơn vị tháng. Trường SPP_Term của BC1. PHÁI SINH, cùng cơ chế JOIN với SPP_AMOUNT: E.TERM hoặc F/G/H/I.TIME_VALID của đúng bảng đã khớp điều kiện JOIN.</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>CASE A.SUB_PRODUCT_LINE WHEN 'Thẻ tín dụng' THEN E.TERM WHEN 'SeABuy' THEN F.TIME_VALID WHEN 'SeACivil' THEN G.TIME_VALID WHEN 'SeATeacher' THEN H.TIME_VALID WHEN 'SeAWomen' THEN I.TIME_VALID END</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="105" customHeight="1">
+      <c r="A27" s="28" t="inlineStr">
         <is>
           <t>CARD_TYPE_CODE</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B27" s="25" t="inlineStr">
         <is>
           <t>VARCHAR2(100)</t>
         </is>
       </c>
-      <c r="C25" s="26" t="inlineStr">
-        <is>
-          <t>Loại thẻ đăng ký</t>
-        </is>
-      </c>
-      <c r="D25" s="54" t="inlineStr">
-        <is>
-          <t>Loại thẻ đăng ký lúc đề xuất sản phẩm phụ là thẻ tín dụng, chỉ có giá trị ở dòng SUB_PRODUCT_LINE='Thẻ tín dụng' — khác khái niệm BC1.K_TYPE (loại thẻ thật sau giải ngân, nguồn STG_DIM_CARD.K_TYPE qua NG_SB_RLOS_SENT_CBS_LOG, ngoài phạm vi datamart hiện tại)</t>
-        </is>
-      </c>
-      <c r="E25" s="31" t="inlineStr">
-        <is>
-          <t>A.CARD_TYPE_CODE</t>
+      <c r="C27" s="26" t="inlineStr">
+        <is>
+          <t>Loại thẻ đề xuất</t>
+        </is>
+      </c>
+      <c r="D27" s="54" t="inlineStr">
+        <is>
+          <t>Loại thẻ đăng ký lúc đề xuất sản phẩm phụ là thẻ tín dụng. Chỉ có ở dòng SUB_PRODUCT_LINE='Thẻ tín dụng'. Là khái niệm khác BC1.K_TYPE (loại thẻ thật sau giải ngân, nguồn STG_DIM_CARD.K_TYPE qua NG_SB_RLOS_SENT_CBS_LOG — thuộc FCT_RLOS_APPLICATION, không đi qua bảng này, không dùng để tra BC1.K_TYPE). NG_SB_RLOS_SENT_CBS_LOG không liên quan gì tới bảng này.</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>E.CARD_TYPE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="16" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="55" t="inlineStr">
+        <is>
+          <t>Điều kiện join giữa các bảng</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="51" t="n"/>
+      <c r="D30" s="54" t="n"/>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN B.WI_NAME = A.WI_NAME AND v_batch_date BETWEEN B.EFF_DATE AND NVL(B.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1">
+      <c r="A31" s="25" t="n"/>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="51" t="n"/>
+      <c r="D31" s="54" t="n"/>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN C.WI_NAME = A.WI_NAME</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="51" t="n"/>
+      <c r="D32" s="54" t="n"/>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN D.PRODUCTLINE_CODE = C.PRODUCT_LINE AND D.SECONDARY_PRODUCT = A.SUB_PRODUCT_LINE AND v_batch_date BETWEEN D.EFF_DATE AND NVL(D.EXP_DATE, v_batch_date)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="51" t="n"/>
+      <c r="D33" s="54" t="n"/>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN E.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'Thẻ tín dụng'</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="51" t="n"/>
+      <c r="D34" s="54" t="n"/>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN F.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeABuy'</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="A35" s="25" t="n"/>
+      <c r="B35" s="25" t="n"/>
+      <c r="C35" s="51" t="n"/>
+      <c r="D35" s="54" t="n"/>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN G.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeACivil'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="51" t="n"/>
+      <c r="D36" s="54" t="n"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN H.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeATeacher'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="A37" s="25" t="n"/>
+      <c r="B37" s="25" t="n"/>
+      <c r="C37" s="51" t="n"/>
+      <c r="D37" s="54" t="n"/>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>LEFT JOIN I.WI_NAME = A.WI_NAME AND A.SUB_PRODUCT_LINE = 'SeAWomen'</t>
         </is>
       </c>
     </row>
